--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260730.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260730.xlsx
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>10,704,940</t>
+          <t>7,975,532</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>7,975,532</t>
+          <t>10,704,940</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1569,17 +1569,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>202608TX</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>臺股期貨</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>1,828,718</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1591,17 +1591,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>202608TX</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>臺股期貨</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>1,828,718</t>
+          <t>648</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
